--- a/output/2026-09-22/enriched_analysis.xlsx
+++ b/output/2026-09-22/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.641</v>
+        <v>3.626</v>
       </c>
       <c r="W2" t="n">
-        <v>2909</v>
+        <v>2921</v>
       </c>
       <c r="X2" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="X3" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.914</v>
+        <v>0.919</v>
       </c>
       <c r="W4" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X4" t="n">
-        <v>8.98</v>
+        <v>8.93</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.289</v>
+        <v>0.293</v>
       </c>
       <c r="W5" t="n">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="X5" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -2047,25 +2047,25 @@
         <v>662.75</v>
       </c>
       <c r="J7" t="n">
-        <v>625.41</v>
+        <v>630.67</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.96</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>39558097</v>
+        <v>46955184</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>39558097</v>
+        <v>46955184</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2079,15 +2079,15 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.323</v>
+        <v>0.384</v>
       </c>
       <c r="W7" t="n">
         <v>1224</v>
@@ -2129,10 +2129,10 @@
         <v>43</v>
       </c>
       <c r="AJ7" t="n">
-        <v>625.4145705206241</v>
+        <v>630.668797765033</v>
       </c>
       <c r="AK7" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2156,47 +2156,47 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AR7" t="n">
         <v>95</v>
       </c>
       <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3</v>
-      </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AY7" t="n">
-        <v>6266479</v>
+        <v>13663566</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9395107</v>
+        <v>16792194</v>
       </c>
       <c r="BA7" t="n">
-        <v>22368301</v>
+        <v>29765388</v>
       </c>
       <c r="BB7" t="n">
-        <v>28676708</v>
+        <v>36073795</v>
       </c>
       <c r="BC7" t="n">
-        <v>31585748</v>
+        <v>38982835</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>6266479</v>
+        <v>13663566</v>
       </c>
       <c r="BO7" t="n">
-        <v>22368301</v>
+        <v>29765388</v>
       </c>
       <c r="BP7" t="n">
         <v>2</v>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.2801</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="8">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="W8" t="n">
-        <v>1538</v>
+        <v>1521</v>
       </c>
       <c r="X8" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="Y8" t="n">
         <v>55</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.534</v>
       </c>
       <c r="W9" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="X9" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2786,10 +2786,10 @@
         <v>0.111</v>
       </c>
       <c r="W10" t="n">
-        <v>2840</v>
+        <v>2819</v>
       </c>
       <c r="X10" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Y10" t="n">
         <v>-3</v>
@@ -3018,7 +3018,7 @@
         <v>0.367</v>
       </c>
       <c r="W11" t="n">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="X11" t="n">
         <v>21.7</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2.28</v>
+        <v>2.267</v>
       </c>
       <c r="W12" t="n">
-        <v>2613</v>
+        <v>2628</v>
       </c>
       <c r="X12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.155</v>
+        <v>0.16</v>
       </c>
       <c r="W13" t="n">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="X13" t="n">
-        <v>59.8</v>
+        <v>58</v>
       </c>
       <c r="Y13" t="n">
         <v>3</v>
@@ -3714,10 +3714,10 @@
         <v>0.046</v>
       </c>
       <c r="W14" t="n">
-        <v>15704</v>
+        <v>15755</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="Y14" t="n">
         <v>83</v>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1.582</v>
+        <v>1.595</v>
       </c>
       <c r="W15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.102</v>
+        <v>0.101</v>
       </c>
       <c r="W16" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="X16" t="n">
         <v>27</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.489</v>
+        <v>0.496</v>
       </c>
       <c r="W17" t="n">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="X17" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
         <v>-1</v>
@@ -4872,10 +4872,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="X19" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y19" t="n">
         <v>19</v>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="W20" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="X20" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.291</v>
+        <v>0.294</v>
       </c>
       <c r="W21" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X21" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="W22" t="n">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="X22" t="n">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="Y22" t="n">
         <v>118</v>
@@ -5791,13 +5791,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.752</v>
+        <v>1.741</v>
       </c>
       <c r="W23" t="n">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="X23" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y23" t="n">
         <v>30</v>
@@ -6020,10 +6020,10 @@
         <v>0.007</v>
       </c>
       <c r="W24" t="n">
-        <v>5581</v>
+        <v>5587</v>
       </c>
       <c r="X24" t="n">
-        <v>9.449999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Y24" t="n">
         <v>43</v>
@@ -6484,10 +6484,10 @@
         <v>0.054</v>
       </c>
       <c r="W26" t="n">
-        <v>2053</v>
+        <v>2033</v>
       </c>
       <c r="X26" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="Y26" t="n">
         <v>20</v>
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.636</v>
+        <v>0.646</v>
       </c>
       <c r="W28" t="n">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="X28" t="n">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="Y28" t="n">
         <v>-61</v>
@@ -7176,7 +7176,7 @@
         <v>0.095</v>
       </c>
       <c r="W29" t="n">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="X29" t="n">
         <v>14.1</v>
@@ -7408,7 +7408,7 @@
         <v>0.026</v>
       </c>
       <c r="W30" t="n">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.963</v>
+        <v>0.931</v>
       </c>
       <c r="W31" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="X31" t="n">
-        <v>6.03</v>
+        <v>6.24</v>
       </c>
       <c r="Y31" t="n">
         <v>31</v>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="W32" t="n">
-        <v>5001</v>
+        <v>5010</v>
       </c>
       <c r="X32" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="Y32" t="n">
         <v>-25</v>
@@ -8098,10 +8098,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>52703</v>
+        <v>52528</v>
       </c>
       <c r="X33" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="Y33" t="n">
         <v>5</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.479</v>
+        <v>0.486</v>
       </c>
       <c r="W35" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="X35" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="Y35" t="n">
         <v>19</v>
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="X36" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="Y36" t="n">
         <v>185</v>
@@ -9024,10 +9024,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3939</v>
+        <v>3926</v>
       </c>
       <c r="X37" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Y37" t="n">
         <v>42</v>
@@ -9256,7 +9256,7 @@
         <v>0.021</v>
       </c>
       <c r="W38" t="n">
-        <v>9372</v>
+        <v>9414</v>
       </c>
       <c r="X38" t="n">
         <v>12.4</v>
@@ -9488,10 +9488,10 @@
         <v>0.033</v>
       </c>
       <c r="W39" t="n">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="X39" t="n">
-        <v>47.6</v>
+        <v>48.5</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
@@ -9717,13 +9717,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.546</v>
+        <v>0.547</v>
       </c>
       <c r="W40" t="n">
-        <v>3540</v>
+        <v>3535</v>
       </c>
       <c r="X40" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Y40" t="n">
         <v>2</v>
@@ -9952,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="X41" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="Y41" t="n">
         <v>5</v>
@@ -10184,7 +10184,7 @@
         <v>0.128</v>
       </c>
       <c r="W42" t="n">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="X42" t="n">
         <v>13.8</v>
@@ -10411,13 +10411,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.203</v>
+        <v>0.207</v>
       </c>
       <c r="W43" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="X43" t="n">
-        <v>26.3</v>
+        <v>25.8</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10646,7 +10646,7 @@
         <v>0.223</v>
       </c>
       <c r="W44" t="n">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="X44" t="n">
         <v>18.9</v>
@@ -10875,13 +10875,13 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="W45" t="n">
-        <v>1669</v>
+        <v>1680</v>
       </c>
       <c r="X45" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Y45" t="n">
         <v>10</v>
@@ -11107,13 +11107,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="W46" t="n">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="X46" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="Y46" t="n">
         <v>9</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.256</v>
+        <v>0.259</v>
       </c>
       <c r="W47" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="X47" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="Y47" t="n">
         <v>16</v>
@@ -11574,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="X48" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Y48" t="n">
         <v>3</v>
@@ -11806,7 +11806,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>8961</v>
+        <v>8942</v>
       </c>
       <c r="X49" t="n">
         <v>15.2</v>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="W50" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="X50" t="n">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="Y50" t="n">
         <v>246</v>
@@ -12270,7 +12270,7 @@
         <v>0.081</v>
       </c>
       <c r="W51" t="n">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="X51" t="n">
         <v>30.4</v>
@@ -12502,10 +12502,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>116392</v>
+        <v>116622</v>
       </c>
       <c r="X52" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="Y52" t="n">
         <v>18</v>
@@ -12918,23 +12918,23 @@
         <v>662.75</v>
       </c>
       <c r="D7" t="n">
-        <v>625.41</v>
+        <v>630.67</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="F7" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>3.96</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-22/enriched_analysis.xlsx
+++ b/output/2026-09-22/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.626</v>
+        <v>3.667</v>
       </c>
       <c r="W2" t="n">
-        <v>2921</v>
+        <v>2888</v>
       </c>
       <c r="X2" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1164,10 +1164,10 @@
         <v>0.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2630</v>
+        <v>2643</v>
       </c>
       <c r="X3" t="n">
-        <v>9.02</v>
+        <v>9.09</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1353,25 +1353,25 @@
         <v>71.39</v>
       </c>
       <c r="J4" t="n">
-        <v>74.37</v>
+        <v>74.22</v>
       </c>
       <c r="K4" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="L4" t="n">
         <v>72.56999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="N4" t="n">
-        <v>19292727</v>
+        <v>20066329</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>19292727</v>
+        <v>20066329</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1385,21 +1385,21 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.919</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="X4" t="n">
-        <v>8.93</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1435,10 +1435,10 @@
         <v>62.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74.36840887977458</v>
+        <v>74.21830535305453</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1462,47 +1462,47 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AR4" t="n">
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>751503</v>
+        <v>1525105</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6093233</v>
+        <v>6866835</v>
       </c>
       <c r="BA4" t="n">
-        <v>12268290</v>
+        <v>13041892</v>
       </c>
       <c r="BB4" t="n">
-        <v>19292727</v>
+        <v>20066329</v>
       </c>
       <c r="BC4" t="n">
-        <v>19292727</v>
+        <v>20066329</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1535,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>751503</v>
+        <v>1525105</v>
       </c>
       <c r="BO4" t="n">
-        <v>12268290</v>
+        <v>13041892</v>
       </c>
       <c r="BP4" t="n">
         <v>1</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0613</v>
+        <v>0.1169</v>
       </c>
     </row>
     <row r="5">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.293</v>
+        <v>0.299</v>
       </c>
       <c r="W5" t="n">
-        <v>1045</v>
+        <v>1025</v>
       </c>
       <c r="X5" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -2322,10 +2322,10 @@
         <v>0.054</v>
       </c>
       <c r="W8" t="n">
-        <v>1521</v>
+        <v>1510</v>
       </c>
       <c r="X8" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Y8" t="n">
         <v>55</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.534</v>
+        <v>0.555</v>
       </c>
       <c r="W9" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="X9" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="W10" t="n">
-        <v>2819</v>
+        <v>2716</v>
       </c>
       <c r="X10" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="Y10" t="n">
         <v>-3</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.367</v>
+        <v>0.359</v>
       </c>
       <c r="W11" t="n">
-        <v>2646</v>
+        <v>2707</v>
       </c>
       <c r="X11" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="Y11" t="n">
         <v>8</v>
@@ -3407,12 +3407,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3424,210 +3424,210 @@
         </is>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4930.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5198.76</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="W13" t="n">
+        <v>15911</v>
+      </c>
+      <c r="X13" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>5</v>
       </c>
-      <c r="F13" t="n">
-        <v>14</v>
-      </c>
-      <c r="G13" t="n">
-        <v>25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>261.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>243.52</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AG13" t="n">
+        <v>5616.39</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4418.71</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>5198.755988455989</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>19879002</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>19879002</v>
+      </c>
+      <c r="BP13" t="n">
         <v>3</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W13" t="n">
-        <v>694</v>
-      </c>
-      <c r="X13" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>97</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>256.16</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>186.28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>238.0921052631579</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>47</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>18095000</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>18095000</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>2</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -3639,16 +3639,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3656,40 +3656,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4930.5</v>
+        <v>171.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5198.76</v>
+        <v>189.45</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.2</v>
+        <v>-9.5</v>
       </c>
       <c r="L14" t="n">
-        <v>67.16</v>
+        <v>64.08</v>
       </c>
       <c r="M14" t="n">
-        <v>7.21</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>72054758</v>
+        <v>33968886</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>72054758</v>
+        <v>33968886</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3703,60 +3703,60 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.046</v>
+        <v>0.502</v>
       </c>
       <c r="W14" t="n">
-        <v>15755</v>
+        <v>677</v>
       </c>
       <c r="X14" t="n">
-        <v>40.1</v>
+        <v>14.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>83</v>
+        <v>-1</v>
       </c>
       <c r="Z14" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>264</v>
+        <v>45</v>
       </c>
       <c r="AB14" t="n">
-        <v>27.38</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>25.5</v>
+        <v>19.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.64</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>5616.39</v>
+        <v>169.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>4418.71</v>
+        <v>192.53</v>
       </c>
       <c r="AI14" t="n">
-        <v>41.1</v>
+        <v>8.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5198.755988455989</v>
+        <v>189.4527941996654</v>
       </c>
       <c r="AK14" t="n">
-        <v>-5.2</v>
+        <v>-9.5</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3775,22 +3775,22 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AR14" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
@@ -3802,10 +3802,10 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -3814,13 +3814,13 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>19879002</v>
+        <v>8001009</v>
       </c>
       <c r="BB14" t="n">
-        <v>72054758</v>
+        <v>8001009</v>
       </c>
       <c r="BC14" t="n">
-        <v>72054758</v>
+        <v>13998476</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>19879002</v>
+        <v>8001009</v>
       </c>
       <c r="BP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -3871,12 +3871,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3888,40 +3888,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
         <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>58.77</v>
+        <v>261.5</v>
       </c>
       <c r="J15" t="n">
-        <v>53.45</v>
+        <v>243.52</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>67.23</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>19457263</v>
+        <v>11080000</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>19457263</v>
+        <v>11080000</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3935,62 +3935,64 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>1.595</v>
+        <v>0.154</v>
       </c>
       <c r="W15" t="n">
-        <v>122</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="X15" t="n">
+        <v>60.2</v>
+      </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
-        <v>-3779</v>
+        <v>97</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.05</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1.26</v>
+        <v>11.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>3</v>
+        <v>16.21</v>
       </c>
       <c r="AG15" t="n">
-        <v>54.34</v>
+        <v>256.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>55.17</v>
+        <v>186.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.9</v>
+        <v>106.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>53.44741172107844</v>
+        <v>238.0921052631579</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4005,91 +4007,91 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4065000</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4065000</v>
+      </c>
+      <c r="BP15" t="n">
         <v>2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1053004</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2942912</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2942912</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
@@ -4101,16 +4103,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,40 +4120,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H16" t="n">
         <v>-1</v>
       </c>
       <c r="I16" t="n">
-        <v>187.04</v>
+        <v>58.77</v>
       </c>
       <c r="J16" t="n">
-        <v>170.45</v>
+        <v>53.45</v>
       </c>
       <c r="K16" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>67.54000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="M16" t="n">
-        <v>0.26</v>
+        <v>1.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2560187</v>
+        <v>19457263</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2560187</v>
+        <v>19457263</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4165,124 +4167,122 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="W16" t="n">
+        <v>122</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-3779</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>53.44741172107844</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="W16" t="n">
-        <v>253</v>
-      </c>
-      <c r="X16" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-31</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>180.19</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>163.07</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>170.4518641810919</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1053004</v>
       </c>
       <c r="BA16" t="n">
-        <v>5120374</v>
+        <v>2942912</v>
       </c>
       <c r="BB16" t="n">
-        <v>5120374</v>
+        <v>19457263</v>
       </c>
       <c r="BC16" t="n">
-        <v>5120374</v>
+        <v>19457263</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4318,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>5120374</v>
+        <v>2942912</v>
       </c>
       <c r="BP16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
@@ -4333,16 +4333,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4350,40 +4350,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I17" t="n">
-        <v>171.4</v>
+        <v>187.04</v>
       </c>
       <c r="J17" t="n">
-        <v>189.45</v>
+        <v>170.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>64.08</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0.26</v>
       </c>
       <c r="N17" t="n">
-        <v>33968886</v>
+        <v>2560187</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>33968886</v>
+        <v>2560187</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4397,60 +4397,60 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.496</v>
+        <v>0.101</v>
       </c>
       <c r="W17" t="n">
-        <v>685</v>
+        <v>253</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>27.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>45</v>
+        <v>-31</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.3</v>
+        <v>4.96</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>2.97</v>
       </c>
       <c r="AG17" t="n">
-        <v>169.32</v>
+        <v>180.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>192.53</v>
+        <v>163.07</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.4</v>
+        <v>47.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>189.4527941996654</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK17" t="n">
-        <v>-9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
@@ -4469,22 +4469,22 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -4493,13 +4493,13 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>8001009</v>
+        <v>5120374</v>
       </c>
       <c r="BB17" t="n">
-        <v>8001009</v>
+        <v>5120374</v>
       </c>
       <c r="BC17" t="n">
-        <v>13998476</v>
+        <v>5120374</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>8001009</v>
+        <v>5120374</v>
       </c>
       <c r="BP17" t="n">
         <v>2</v>
@@ -4640,10 +4640,10 @@
         <v>0.076</v>
       </c>
       <c r="W18" t="n">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="X18" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="Y18" t="n">
         <v>-8</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>822</v>
+        <v>796</v>
       </c>
       <c r="X19" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="Y19" t="n">
         <v>19</v>
@@ -5027,12 +5027,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5044,40 +5044,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>83.70999999999999</v>
+        <v>141.84</v>
       </c>
       <c r="J20" t="n">
-        <v>81.11</v>
+        <v>144.98</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="L20" t="n">
-        <v>62.78</v>
+        <v>63.69</v>
       </c>
       <c r="M20" t="n">
-        <v>1.85</v>
+        <v>15.95</v>
       </c>
       <c r="N20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5091,60 +5091,54 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.436</v>
+        <v>2.335</v>
       </c>
       <c r="W20" t="n">
-        <v>425</v>
+        <v>683</v>
       </c>
       <c r="X20" t="n">
-        <v>39.4</v>
+        <v>25.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.390000000000001</v>
+        <v>39</v>
       </c>
       <c r="AA20" t="n">
-        <v>-19</v>
+        <v>30</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.54</v>
+        <v>7.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.73</v>
+        <v>14.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>77.34999999999999</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>77.95</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>12.7</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="n">
-        <v>81.11201466291054</v>
+        <v>144.9806581818182</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -5153,62 +5147,62 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
         <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>159478724</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3590835</v>
+        <v>159478724</v>
       </c>
       <c r="BA20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="BB20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="BC20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5241,10 +5235,10 @@
         <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>159478724</v>
       </c>
       <c r="BO20" t="n">
-        <v>18542531</v>
+        <v>159478724</v>
       </c>
       <c r="BP20" t="n">
         <v>1</v>
@@ -5253,22 +5247,22 @@
         <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5276,107 +5270,107 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>81.11</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18542531</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>18542531</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="W21" t="n">
+        <v>420</v>
+      </c>
+      <c r="X21" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y21" t="n">
         <v>21</v>
       </c>
-      <c r="H21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>219.54</v>
-      </c>
-      <c r="J21" t="n">
-        <v>210</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L21" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S21" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>12</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="W21" t="n">
-        <v>202</v>
-      </c>
-      <c r="X21" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>12</v>
-      </c>
       <c r="Z21" t="n">
-        <v>0.03</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>16</v>
+        <v>-19</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.03</v>
+        <v>1.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.91</v>
+        <v>8.73</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.16</v>
+        <v>41.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>210.17</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="AH21" t="n">
-        <v>195.87</v>
+        <v>77.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>19.5</v>
+        <v>12.7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>210.0036030944223</v>
+        <v>81.11201466291054</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5395,52 +5389,52 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>729101</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2798008</v>
+        <v>3590835</v>
       </c>
       <c r="BA21" t="n">
-        <v>3763406</v>
+        <v>18542531</v>
       </c>
       <c r="BB21" t="n">
-        <v>5944992</v>
+        <v>18542531</v>
       </c>
       <c r="BC21" t="n">
-        <v>5944992</v>
+        <v>18542531</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5473,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>729101</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>3763406</v>
+        <v>18542531</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5485,22 +5479,22 @@
         <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>0.1937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,40 +5502,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I22" t="n">
-        <v>19.38</v>
+        <v>219.54</v>
       </c>
       <c r="J22" t="n">
-        <v>21.01</v>
+        <v>210</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.8</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>70.87</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="N22" t="n">
-        <v>4960333</v>
+        <v>5944992</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4960333</v>
+        <v>5944992</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -5555,120 +5549,124 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.136</v>
+        <v>0.294</v>
       </c>
       <c r="W22" t="n">
-        <v>365</v>
+        <v>202</v>
       </c>
       <c r="X22" t="n">
-        <v>5.88</v>
+        <v>25.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z22" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.03</v>
+      </c>
       <c r="AA22" t="n">
-        <v>391</v>
+        <v>16</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>18.5</v>
+        <v>7.91</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
+      <c r="AF22" t="n">
+        <v>3.16</v>
+      </c>
       <c r="AG22" t="n">
-        <v>19.29</v>
+        <v>210.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.39</v>
+        <v>195.87</v>
       </c>
       <c r="AI22" t="n">
-        <v>44.3</v>
+        <v>19.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21.00741139152052</v>
+        <v>210.0036030944223</v>
       </c>
       <c r="AK22" t="n">
-        <v>-7.7</v>
+        <v>4.5</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>35</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT22" t="n">
         <v>2</v>
       </c>
-      <c r="AR22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>729101</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2798008</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3763406</v>
       </c>
       <c r="BB22" t="n">
-        <v>4960333</v>
+        <v>5944992</v>
       </c>
       <c r="BC22" t="n">
-        <v>4960333</v>
+        <v>5944992</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -5701,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>729101</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>3763406</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
@@ -5713,18 +5711,18 @@
         <v>0</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>0.1937</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5736,40 +5734,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>141.84</v>
+        <v>19.38</v>
       </c>
       <c r="J23" t="n">
-        <v>146.47</v>
+        <v>21.01</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="L23" t="n">
-        <v>63.69</v>
+        <v>70.87</v>
       </c>
       <c r="M23" t="n">
-        <v>11.72</v>
+        <v>0.5</v>
       </c>
       <c r="N23" t="n">
-        <v>117176839</v>
+        <v>4960333</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>117176839</v>
+        <v>4960333</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -5783,118 +5781,120 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.741</v>
+        <v>0.136</v>
       </c>
       <c r="W23" t="n">
-        <v>673</v>
+        <v>365</v>
       </c>
       <c r="X23" t="n">
-        <v>25.3</v>
+        <v>5.88</v>
       </c>
       <c r="Y23" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>39</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>30</v>
+        <v>391</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.88</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>14.1</v>
+        <v>18.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>44.3</v>
+      </c>
       <c r="AJ23" t="n">
-        <v>146.47104875</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK23" t="n">
-        <v>-3.2</v>
+        <v>-7.7</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR23" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY23" t="n">
-        <v>117176839</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>117176839</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>117176839</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>117176839</v>
+        <v>4960333</v>
       </c>
       <c r="BC23" t="n">
-        <v>117176839</v>
+        <v>4960333</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
@@ -5927,10 +5927,10 @@
         <v>0</v>
       </c>
       <c r="BN23" t="n">
-        <v>117176839</v>
+        <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>117176839</v>
+        <v>0</v>
       </c>
       <c r="BP23" t="n">
         <v>1</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="BR23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6020,10 +6020,10 @@
         <v>0.007</v>
       </c>
       <c r="W24" t="n">
-        <v>5587</v>
+        <v>5540</v>
       </c>
       <c r="X24" t="n">
-        <v>9.460000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="Y24" t="n">
         <v>43</v>
@@ -6252,10 +6252,10 @@
         <v>0.038</v>
       </c>
       <c r="W25" t="n">
-        <v>3563</v>
+        <v>3539</v>
       </c>
       <c r="X25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
         <v>-4</v>
@@ -6481,13 +6481,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="W26" t="n">
-        <v>2033</v>
+        <v>1972</v>
       </c>
       <c r="X26" t="n">
-        <v>46.7</v>
+        <v>45.3</v>
       </c>
       <c r="Y26" t="n">
         <v>20</v>
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.646</v>
+        <v>0.643</v>
       </c>
       <c r="W28" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="X28" t="n">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="Y28" t="n">
         <v>-61</v>
@@ -7101,12 +7101,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7118,40 +7118,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I29" t="n">
-        <v>275.25</v>
+        <v>50.47</v>
       </c>
       <c r="J29" t="n">
-        <v>269.7</v>
+        <v>55.69</v>
       </c>
       <c r="K29" t="n">
-        <v>2.1</v>
+        <v>-9.4</v>
       </c>
       <c r="L29" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="N29" t="n">
-        <v>14833500</v>
+        <v>24004853</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>14833500</v>
+        <v>24004853</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7165,124 +7165,124 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.095</v>
+        <v>0.543</v>
       </c>
       <c r="W29" t="n">
-        <v>1554</v>
+        <v>442</v>
       </c>
       <c r="X29" t="n">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>56.41323055518416</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ29" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW29" t="n">
         <v>6</v>
       </c>
-      <c r="Z29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>267.86</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>287.83</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>29112781</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>29112781</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7315,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7327,22 +7327,22 @@
         <v>0</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7350,40 +7350,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>598.1</v>
+        <v>275.25</v>
       </c>
       <c r="J30" t="n">
-        <v>593.62</v>
+        <v>269.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="L30" t="n">
-        <v>74.02</v>
+        <v>73.09</v>
       </c>
       <c r="M30" t="n">
-        <v>0.25</v>
+        <v>1.48</v>
       </c>
       <c r="N30" t="n">
-        <v>2458195</v>
+        <v>14833500</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2458195</v>
+        <v>14833500</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7397,122 +7397,124 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.026</v>
+        <v>0.096</v>
       </c>
       <c r="W30" t="n">
-        <v>944</v>
-      </c>
-      <c r="X30" t="inlineStr"/>
+        <v>1553</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.1</v>
+      </c>
       <c r="Y30" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="AA30" t="n">
-        <v>-152</v>
+        <v>18</v>
       </c>
       <c r="AB30" t="n">
-        <v>-6.5</v>
+        <v>4.31</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.24</v>
+        <v>13.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.23</v>
+        <v>0.28</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>590.6900000000001</v>
+        <v>267.86</v>
       </c>
       <c r="AH30" t="n">
-        <v>546.09</v>
+        <v>287.83</v>
       </c>
       <c r="AI30" t="n">
-        <v>20.8</v>
+        <v>10.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>593.6235208886742</v>
+        <v>269.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="AS30" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>322003</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7548,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BP30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ30" t="n">
         <v>0</v>
@@ -7563,12 +7565,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7580,40 +7582,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>132.5</v>
+        <v>598.1</v>
       </c>
       <c r="J31" t="n">
-        <v>132.2</v>
+        <v>593.62</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="L31" t="n">
-        <v>67.83</v>
+        <v>74.02</v>
       </c>
       <c r="M31" t="n">
-        <v>1.98</v>
+        <v>0.25</v>
       </c>
       <c r="N31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -7631,92 +7633,94 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.931</v>
+        <v>0.024</v>
       </c>
       <c r="W31" t="n">
-        <v>213</v>
-      </c>
-      <c r="X31" t="n">
-        <v>6.24</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z31" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
       <c r="AA31" t="n">
-        <v>35</v>
+        <v>-152</v>
       </c>
       <c r="AB31" t="n">
-        <v>5.39</v>
+        <v>-6.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.8</v>
+        <v>9.24</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.89</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>6</v>
+      </c>
       <c r="AG31" t="n">
-        <v>260.12</v>
+        <v>590.6900000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>272.11</v>
+        <v>546.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>-49.1</v>
+        <v>20.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>132.2027333333333</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AR31" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AT31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
         <v>3</v>
@@ -7728,19 +7732,19 @@
         <v>3</v>
       </c>
       <c r="AY31" t="n">
-        <v>10052740</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19830410</v>
+        <v>322003</v>
       </c>
       <c r="BA31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="BB31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="BC31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -7773,34 +7777,34 @@
         <v>0</v>
       </c>
       <c r="BN31" t="n">
-        <v>10052740</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>19830410</v>
+        <v>2458195</v>
       </c>
       <c r="BP31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BQ31" t="n">
         <v>0</v>
       </c>
       <c r="BR31" t="n">
-        <v>0.5069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7808,40 +7812,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>123.22</v>
+        <v>132.5</v>
       </c>
       <c r="J32" t="n">
-        <v>105.19</v>
+        <v>132.2</v>
       </c>
       <c r="K32" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="L32" t="n">
-        <v>67.15000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="M32" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="N32" t="n">
-        <v>26297500</v>
+        <v>19830410</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>26297500</v>
+        <v>19830410</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7855,124 +7859,120 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.052</v>
+        <v>0.874</v>
       </c>
       <c r="W32" t="n">
-        <v>5010</v>
+        <v>227</v>
       </c>
       <c r="X32" t="n">
-        <v>32.7</v>
+        <v>6.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>-25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>71</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>-11</v>
+        <v>35</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.48</v>
+        <v>5.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.7</v>
+        <v>11.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>69</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="n">
-        <v>111.73</v>
+        <v>260.12</v>
       </c>
       <c r="AH32" t="n">
-        <v>112.05</v>
+        <v>272.11</v>
       </c>
       <c r="AI32" t="n">
-        <v>37.1</v>
+        <v>-49.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>105.19</v>
+        <v>132.2027333333333</v>
       </c>
       <c r="AK32" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="AS32" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX32" t="n">
         <v>3</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>10052740</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="BC32" t="n">
-        <v>78892500</v>
+        <v>19830410</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8005,19 +8005,19 @@
         <v>0</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>10052740</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>19830410</v>
       </c>
       <c r="BP32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ32" t="n">
         <v>0</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>0.5069</v>
       </c>
     </row>
     <row r="33">
@@ -8098,10 +8098,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>52528</v>
+        <v>53041</v>
       </c>
       <c r="X33" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="Y33" t="n">
         <v>5</v>
@@ -8255,12 +8255,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8272,40 +8272,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>168.63</v>
+        <v>123.22</v>
       </c>
       <c r="J34" t="n">
-        <v>166.77</v>
+        <v>105.19</v>
       </c>
       <c r="K34" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="L34" t="n">
-        <v>61.48</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4</v>
+        <v>2.63</v>
       </c>
       <c r="N34" t="n">
-        <v>3987724</v>
+        <v>26297500</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3987724</v>
+        <v>26297500</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -8319,124 +8319,124 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.195</v>
+        <v>0.053</v>
       </c>
       <c r="W34" t="n">
-        <v>204</v>
+        <v>4999</v>
       </c>
       <c r="X34" t="n">
-        <v>35.4</v>
+        <v>32.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>-44</v>
+        <v>-25</v>
       </c>
       <c r="Z34" t="n">
-        <v>-3.28</v>
+        <v>71</v>
       </c>
       <c r="AA34" t="n">
-        <v>141</v>
+        <v>-11</v>
       </c>
       <c r="AB34" t="n">
-        <v>-4.05</v>
+        <v>1.48</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.25</v>
+        <v>10.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>-35.96</v>
+        <v>69</v>
       </c>
       <c r="AG34" t="n">
-        <v>176.13</v>
+        <v>111.73</v>
       </c>
       <c r="AH34" t="n">
-        <v>179.98</v>
+        <v>112.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>11.2</v>
+        <v>37.1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>166.7666443626631</v>
+        <v>105.19</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="AS34" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="AT34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>3987724</v>
+        <v>78892500</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -8469,10 +8469,10 @@
         <v>0</v>
       </c>
       <c r="BN34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="BO34" t="n">
-        <v>3987724</v>
+        <v>0</v>
       </c>
       <c r="BP34" t="n">
         <v>1</v>
@@ -8481,18 +8481,18 @@
         <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -8504,40 +8504,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
         <v>-1</v>
       </c>
       <c r="I35" t="n">
-        <v>50.47</v>
+        <v>168.63</v>
       </c>
       <c r="J35" t="n">
-        <v>56.04</v>
+        <v>166.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.9</v>
+        <v>1.1</v>
       </c>
       <c r="L35" t="n">
-        <v>73.01000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="M35" t="n">
-        <v>2.19</v>
+        <v>0.4</v>
       </c>
       <c r="N35" t="n">
-        <v>21940362</v>
+        <v>3987724</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>21940362</v>
+        <v>3987724</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -8559,52 +8559,52 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.486</v>
+        <v>0.198</v>
       </c>
       <c r="W35" t="n">
-        <v>451</v>
+        <v>201</v>
       </c>
       <c r="X35" t="n">
-        <v>11.3</v>
+        <v>34.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>19</v>
+        <v>-44</v>
       </c>
       <c r="Z35" t="n">
-        <v>21</v>
+        <v>-3.28</v>
       </c>
       <c r="AA35" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.22</v>
+        <v>-4.05</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
+        <v>8.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.4</v>
+        <v>-35.96</v>
       </c>
       <c r="AG35" t="n">
-        <v>56.58</v>
+        <v>176.13</v>
       </c>
       <c r="AH35" t="n">
-        <v>58.24</v>
+        <v>179.98</v>
       </c>
       <c r="AI35" t="n">
-        <v>-15.7</v>
+        <v>11.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>56.76403555898796</v>
+        <v>166.7666443626631</v>
       </c>
       <c r="AK35" t="n">
-        <v>-11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -8613,17 +8613,17 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -8632,43 +8632,43 @@
         </is>
       </c>
       <c r="AQ35" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="AR35" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AS35" t="n">
         <v>4</v>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY35" t="n">
-        <v>2958659</v>
+        <v>3987724</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2958659</v>
+        <v>3987724</v>
       </c>
       <c r="BA35" t="n">
-        <v>2958659</v>
+        <v>3987724</v>
       </c>
       <c r="BB35" t="n">
-        <v>27048290</v>
+        <v>3987724</v>
       </c>
       <c r="BC35" t="n">
-        <v>27048290</v>
+        <v>3987724</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8701,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="BN35" t="n">
-        <v>2958659</v>
+        <v>3987724</v>
       </c>
       <c r="BO35" t="n">
-        <v>2958659</v>
+        <v>3987724</v>
       </c>
       <c r="BP35" t="n">
         <v>1</v>
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="X36" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="Y36" t="n">
         <v>185</v>
@@ -9024,10 +9024,10 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3926</v>
+        <v>3958</v>
       </c>
       <c r="X37" t="n">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Y37" t="n">
         <v>42</v>
@@ -9256,7 +9256,7 @@
         <v>0.021</v>
       </c>
       <c r="W38" t="n">
-        <v>9414</v>
+        <v>9339</v>
       </c>
       <c r="X38" t="n">
         <v>12.4</v>
@@ -9485,13 +9485,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="W39" t="n">
-        <v>744</v>
+        <v>718</v>
       </c>
       <c r="X39" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="Y39" t="n">
         <v>7</v>
@@ -9717,13 +9717,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.547</v>
+        <v>0.543</v>
       </c>
       <c r="W40" t="n">
-        <v>3535</v>
+        <v>3559</v>
       </c>
       <c r="X40" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Y40" t="n">
         <v>2</v>
@@ -9952,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="X41" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="Y41" t="n">
         <v>5</v>
@@ -10187,7 +10187,7 @@
         <v>582</v>
       </c>
       <c r="X42" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y42" t="n">
         <v>61</v>
@@ -10643,13 +10643,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.223</v>
+        <v>0.225</v>
       </c>
       <c r="W44" t="n">
-        <v>1789</v>
+        <v>1776</v>
       </c>
       <c r="X44" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="Y44" t="n">
         <v>-3</v>
@@ -10875,13 +10875,13 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="W45" t="n">
-        <v>1680</v>
+        <v>1654</v>
       </c>
       <c r="X45" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="Y45" t="n">
         <v>10</v>
@@ -11107,13 +11107,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="W46" t="n">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="X46" t="n">
-        <v>26.3</v>
+        <v>26.6</v>
       </c>
       <c r="Y46" t="n">
         <v>9</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.259</v>
+        <v>0.255</v>
       </c>
       <c r="W47" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="X47" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="Y47" t="n">
         <v>16</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="X48" t="n">
         <v>689</v>
@@ -11806,7 +11806,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>8942</v>
+        <v>8937</v>
       </c>
       <c r="X49" t="n">
         <v>15.2</v>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>0.356</v>
+        <v>0.349</v>
       </c>
       <c r="W50" t="n">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="X50" t="n">
-        <v>97.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="Y50" t="n">
         <v>246</v>
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="W51" t="n">
-        <v>1684</v>
+        <v>1664</v>
       </c>
       <c r="X51" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="Y51" t="n">
         <v>39</v>
@@ -12502,10 +12502,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>116622</v>
+        <v>116137</v>
       </c>
       <c r="X52" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="Y52" t="n">
         <v>18</v>
@@ -12813,23 +12813,23 @@
         <v>71.39</v>
       </c>
       <c r="D4" t="n">
-        <v>74.37</v>
+        <v>74.22</v>
       </c>
       <c r="E4" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="F4" t="n">
         <v>72.56999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
@@ -13116,175 +13116,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>261.5</v>
+        <v>4930.5</v>
       </c>
       <c r="D13" t="n">
-        <v>243.52</v>
+        <v>5198.76</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4</v>
+        <v>-5.2</v>
       </c>
       <c r="F13" t="n">
-        <v>67.65000000000001</v>
+        <v>67.16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.11</v>
+        <v>7.21</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4930.5</v>
+        <v>171.4</v>
       </c>
       <c r="D14" t="n">
-        <v>5198.76</v>
+        <v>189.45</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2</v>
+        <v>-9.5</v>
       </c>
       <c r="F14" t="n">
-        <v>67.16</v>
+        <v>64.08</v>
       </c>
       <c r="G14" t="n">
-        <v>7.21</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>58.77</v>
+        <v>261.5</v>
       </c>
       <c r="D15" t="n">
-        <v>53.45</v>
+        <v>243.52</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="F15" t="n">
-        <v>67.23</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>187.04</v>
+        <v>58.77</v>
       </c>
       <c r="D16" t="n">
-        <v>170.45</v>
+        <v>53.45</v>
       </c>
       <c r="E16" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>67.54000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.26</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>171.4</v>
+        <v>187.04</v>
       </c>
       <c r="D17" t="n">
-        <v>189.45</v>
+        <v>170.45</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>64.08</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>0.26</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
@@ -13361,140 +13361,140 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>83.70999999999999</v>
+        <v>141.84</v>
       </c>
       <c r="D20" t="n">
-        <v>81.11</v>
+        <v>144.98</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="F20" t="n">
-        <v>62.78</v>
+        <v>63.69</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>15.95</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>219.54</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>210</v>
+        <v>81.11</v>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="n">
-        <v>67.04000000000001</v>
+        <v>62.78</v>
       </c>
       <c r="G21" t="n">
-        <v>0.59</v>
+        <v>1.85</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19.38</v>
+        <v>219.54</v>
       </c>
       <c r="D22" t="n">
-        <v>21.01</v>
+        <v>210</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.8</v>
+        <v>4.5</v>
       </c>
       <c r="F22" t="n">
-        <v>70.87</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>141.84</v>
+        <v>19.38</v>
       </c>
       <c r="D23" t="n">
-        <v>146.47</v>
+        <v>21.01</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="F23" t="n">
-        <v>63.69</v>
+        <v>70.87</v>
       </c>
       <c r="G23" t="n">
-        <v>11.72</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
@@ -13676,140 +13676,140 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>275.25</v>
+        <v>50.47</v>
       </c>
       <c r="D29" t="n">
-        <v>269.7</v>
+        <v>55.69</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1</v>
+        <v>-9.4</v>
       </c>
       <c r="F29" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>598.1</v>
+        <v>275.25</v>
       </c>
       <c r="D30" t="n">
-        <v>593.62</v>
+        <v>269.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="F30" t="n">
-        <v>74.02</v>
+        <v>73.09</v>
       </c>
       <c r="G30" t="n">
-        <v>0.25</v>
+        <v>1.48</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>132.5</v>
+        <v>598.1</v>
       </c>
       <c r="D31" t="n">
-        <v>132.2</v>
+        <v>593.62</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>67.83</v>
+        <v>74.02</v>
       </c>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>123.22</v>
+        <v>132.5</v>
       </c>
       <c r="D32" t="n">
-        <v>105.19</v>
+        <v>132.2</v>
       </c>
       <c r="E32" t="n">
-        <v>17.1</v>
+        <v>0.2</v>
       </c>
       <c r="F32" t="n">
-        <v>67.15000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="G32" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
@@ -13851,63 +13851,63 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>168.63</v>
+        <v>123.22</v>
       </c>
       <c r="D34" t="n">
-        <v>166.77</v>
+        <v>105.19</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="F34" t="n">
-        <v>61.48</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4</v>
+        <v>2.63</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50.47</v>
+        <v>168.63</v>
       </c>
       <c r="D35" t="n">
-        <v>56.04</v>
+        <v>166.77</v>
       </c>
       <c r="E35" t="n">
-        <v>-9.9</v>
+        <v>1.1</v>
       </c>
       <c r="F35" t="n">
-        <v>73.01000000000001</v>
+        <v>61.48</v>
       </c>
       <c r="G35" t="n">
-        <v>2.19</v>
+        <v>0.4</v>
       </c>
       <c r="H35" t="n">
         <v>4</v>

--- a/output/2026-09-22/enriched_analysis.xlsx
+++ b/output/2026-09-22/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.674</v>
+        <v>3.681</v>
       </c>
       <c r="W2" t="n">
-        <v>2883</v>
+        <v>2877</v>
       </c>
       <c r="X2" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.956</v>
       </c>
       <c r="W4" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="X4" t="n">
-        <v>9.140000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="W5" t="n">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="X5" t="n">
         <v>10.1</v>
@@ -2322,10 +2322,10 @@
         <v>0.054</v>
       </c>
       <c r="W8" t="n">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="X8" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="Y8" t="n">
         <v>55</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="W11" t="n">
-        <v>2706</v>
+        <v>2690</v>
       </c>
       <c r="X11" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>8</v>
@@ -3407,12 +3407,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3424,40 +3424,40 @@
         </is>
       </c>
       <c r="E13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="F13" t="n">
-        <v>14</v>
-      </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I13" t="n">
-        <v>260.4</v>
+        <v>58.16</v>
       </c>
       <c r="J13" t="n">
-        <v>243.52</v>
+        <v>53.59</v>
       </c>
       <c r="K13" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="L13" t="n">
-        <v>67.65000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>2.01</v>
       </c>
       <c r="N13" t="n">
-        <v>11080000</v>
+        <v>20124583</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>11080000</v>
+        <v>20124583</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3471,124 +3471,122 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="W13" t="n">
+        <v>124</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-3779</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="W13" t="n">
-        <v>688</v>
-      </c>
-      <c r="X13" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AG13" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>53.58738852926531</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
         <v>3</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>97</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>256.26</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>186.83</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>101.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>238.0921052631579</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>47</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>667320</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1720324</v>
       </c>
       <c r="BA13" t="n">
-        <v>4065000</v>
+        <v>3610232</v>
       </c>
       <c r="BB13" t="n">
-        <v>18095000</v>
+        <v>20124583</v>
       </c>
       <c r="BC13" t="n">
-        <v>18095000</v>
+        <v>20124583</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -3621,30 +3619,30 @@
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>667320</v>
       </c>
       <c r="BO13" t="n">
-        <v>4065000</v>
+        <v>3610232</v>
       </c>
       <c r="BP13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>0.1848</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3656,40 +3654,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5119.5</v>
+        <v>260.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5198.76</v>
+        <v>243.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5</v>
+        <v>6.9</v>
       </c>
       <c r="L14" t="n">
-        <v>67.16</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>7.21</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>72054758</v>
+        <v>11080000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>72054758</v>
+        <v>11080000</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3703,163 +3701,163 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.045</v>
+        <v>0.161</v>
       </c>
       <c r="W14" t="n">
-        <v>15914</v>
+        <v>688</v>
       </c>
       <c r="X14" t="n">
-        <v>40.5</v>
+        <v>57.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>145</v>
+        <v>2.99</v>
       </c>
       <c r="AA14" t="n">
-        <v>264</v>
+        <v>97</v>
       </c>
       <c r="AB14" t="n">
-        <v>27.38</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>25.5</v>
+        <v>11.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>256.26</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>186.83</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>238.0921052631579</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="n">
         <v>5</v>
       </c>
-      <c r="AG14" t="n">
-        <v>5594.12</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>4428.04</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5198.755988455989</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>49</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
+      <c r="AX14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4065000</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>18095000</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>4065000</v>
+      </c>
+      <c r="BP14" t="n">
         <v>2</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>19879002</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>72054758</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>19879002</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>3</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -3871,16 +3869,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3888,208 +3886,210 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
+        <v>27</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5119.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5198.76</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="W15" t="n">
+        <v>15915</v>
+      </c>
+      <c r="X15" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>145</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>264</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
-        <v>21</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>58.16</v>
-      </c>
-      <c r="J15" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>67.23</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="N15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S15" t="b">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>1.569</v>
-      </c>
-      <c r="W15" t="n">
-        <v>124</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
+      <c r="AG15" t="n">
+        <v>5594.12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>4428.04</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>5198.755988455989</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>04-08-2026</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW15" t="n">
         <v>6</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-3779</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AX15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>19879002</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>72054758</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>19879002</v>
+      </c>
+      <c r="BP15" t="n">
         <v>3</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>54.43</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>53.44741172107844</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ15" t="n">
-        <v>41</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1053004</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2942912</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>19457263</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2942912</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="W16" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="X16" t="n">
-        <v>27</v>
+        <v>27.6</v>
       </c>
       <c r="Y16" t="n">
         <v>24</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="W17" t="n">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="X17" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
         <v>-8</v>
@@ -5093,13 +5093,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="W20" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="X20" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.297</v>
+        <v>0.293</v>
       </c>
       <c r="W21" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="X21" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -7178,10 +7178,10 @@
         <v>0.137</v>
       </c>
       <c r="W29" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="X29" t="n">
-        <v>5.87</v>
+        <v>5.85</v>
       </c>
       <c r="Y29" t="n">
         <v>118</v>
@@ -7331,12 +7331,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -7348,40 +7348,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>272.8</v>
+        <v>201.07</v>
       </c>
       <c r="J30" t="n">
-        <v>269.7</v>
+        <v>191.87</v>
       </c>
       <c r="K30" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
-        <v>73.09</v>
+        <v>70.02</v>
       </c>
       <c r="M30" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="N30" t="n">
-        <v>14833500</v>
+        <v>13430794</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>14833500</v>
+        <v>13430794</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7395,94 +7395,94 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.096</v>
+        <v>0.038</v>
       </c>
       <c r="W30" t="n">
-        <v>1547</v>
+        <v>3528</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>20.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="Z30" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AA30" t="n">
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.31</v>
+        <v>2.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>13.6</v>
+        <v>20.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>267.94</v>
+        <v>208.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>287.46</v>
+        <v>193.87</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.5</v>
+        <v>31.7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>269.7</v>
+        <v>191.8684857142857</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR30" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="AS30" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
@@ -7491,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -7506,13 +7506,13 @@
         <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BP30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ30" t="n">
         <v>0</v>
@@ -7563,12 +7563,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7580,171 +7580,171 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14833500</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>14833500</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1547</v>
+      </c>
+      <c r="X31" t="n">
         <v>14</v>
       </c>
-      <c r="F31" t="n">
-        <v>19</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>51.92</v>
-      </c>
-      <c r="J31" t="n">
-        <v>55.69</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="L31" t="n">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N31" t="n">
-        <v>24004853</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>24004853</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>5</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="W31" t="n">
-        <v>452</v>
-      </c>
-      <c r="X31" t="n">
-        <v>11.3</v>
-      </c>
       <c r="Y31" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.22</v>
+        <v>4.31</v>
       </c>
       <c r="AC31" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
         <v>12</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AG31" t="n">
-        <v>56.45</v>
+        <v>267.94</v>
       </c>
       <c r="AH31" t="n">
-        <v>58.17</v>
+        <v>287.46</v>
       </c>
       <c r="AI31" t="n">
-        <v>-13</v>
+        <v>4.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>56.41323055518416</v>
+        <v>269.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>-8</v>
+        <v>1.1</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AS31" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AT31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>5023150</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5023150</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>5023150</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>29112781</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>29112781</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -7777,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="BN31" t="n">
-        <v>5023150</v>
+        <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>5023150</v>
+        <v>0</v>
       </c>
       <c r="BP31" t="n">
         <v>1</v>
@@ -7789,18 +7789,18 @@
         <v>0</v>
       </c>
       <c r="BR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7812,40 +7812,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I32" t="n">
-        <v>201.07</v>
+        <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>191.87</v>
+        <v>55.69</v>
       </c>
       <c r="K32" t="n">
-        <v>4.8</v>
+        <v>-6.8</v>
       </c>
       <c r="L32" t="n">
-        <v>70.02</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="N32" t="n">
-        <v>13430794</v>
+        <v>24004853</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13430794</v>
+        <v>24004853</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7859,64 +7859,64 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.038</v>
+        <v>0.531</v>
       </c>
       <c r="W32" t="n">
-        <v>3528</v>
+        <v>452</v>
       </c>
       <c r="X32" t="n">
-        <v>20.9</v>
+        <v>11.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>-4</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
-        <v>-9</v>
+        <v>20</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>20.8</v>
+        <v>12</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>208.08</v>
+        <v>56.45</v>
       </c>
       <c r="AH32" t="n">
-        <v>193.87</v>
+        <v>58.17</v>
       </c>
       <c r="AI32" t="n">
-        <v>31.7</v>
+        <v>-13</v>
       </c>
       <c r="AJ32" t="n">
-        <v>191.8684857142857</v>
+        <v>56.41323055518416</v>
       </c>
       <c r="AK32" t="n">
-        <v>4.8</v>
+        <v>-8</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -7931,52 +7931,52 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" t="n">
         <v>2</v>
       </c>
-      <c r="AR32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BA32" t="n">
-        <v>13430794</v>
+        <v>5023150</v>
       </c>
       <c r="BB32" t="n">
-        <v>13430794</v>
+        <v>29112781</v>
       </c>
       <c r="BC32" t="n">
-        <v>13430794</v>
+        <v>29112781</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8009,19 +8009,19 @@
         <v>0</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>5023150</v>
       </c>
       <c r="BO32" t="n">
-        <v>13430794</v>
+        <v>5023150</v>
       </c>
       <c r="BP32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ32" t="n">
         <v>0</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -8102,10 +8102,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>53024</v>
+        <v>52756</v>
       </c>
       <c r="X33" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="Y33" t="n">
         <v>5</v>
@@ -8796,10 +8796,10 @@
         <v>0.021</v>
       </c>
       <c r="W36" t="n">
-        <v>9342</v>
+        <v>9347</v>
       </c>
       <c r="X36" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="Y36" t="n">
         <v>-12</v>
@@ -9257,13 +9257,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.639</v>
+        <v>0.641</v>
       </c>
       <c r="W38" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="X38" t="n">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="Y38" t="n">
         <v>-61</v>
@@ -9952,7 +9952,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X41" t="n">
         <v>11.3</v>
@@ -10643,13 +10643,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="W44" t="n">
-        <v>1776</v>
+        <v>1783</v>
       </c>
       <c r="X44" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y44" t="n">
         <v>-3</v>
@@ -11067,25 +11067,25 @@
         <v>95.14</v>
       </c>
       <c r="J46" t="n">
-        <v>98.83</v>
+        <v>97.5</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.7</v>
+        <v>-2.4</v>
       </c>
       <c r="L46" t="n">
         <v>71.89</v>
       </c>
       <c r="M46" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="N46" t="n">
-        <v>12463079</v>
+        <v>22533629</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>12463079</v>
+        <v>22533629</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -11099,15 +11099,15 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.129</v>
+        <v>0.234</v>
       </c>
       <c r="W46" t="n">
         <v>964</v>
@@ -11149,10 +11149,10 @@
         <v>0.6</v>
       </c>
       <c r="AJ46" t="n">
-        <v>98.83018254484323</v>
+        <v>97.50343565290386</v>
       </c>
       <c r="AK46" t="n">
-        <v>-3.7</v>
+        <v>-2.4</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -11176,47 +11176,47 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ46" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AR46" t="n">
         <v>90</v>
       </c>
       <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX46" t="n">
         <v>4</v>
       </c>
-      <c r="AT46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>3</v>
-      </c>
       <c r="AY46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="AZ46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="BA46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="BB46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="BC46" t="n">
-        <v>10363879</v>
+        <v>20434429</v>
       </c>
       <c r="BD46" t="n">
         <v>0</v>
@@ -11249,10 +11249,10 @@
         <v>0</v>
       </c>
       <c r="BN46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="BO46" t="n">
-        <v>9750000</v>
+        <v>19820550</v>
       </c>
       <c r="BP46" t="n">
         <v>1</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="W47" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="X47" t="n">
-        <v>99</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="Y47" t="n">
         <v>246</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="X48" t="n">
         <v>689</v>
@@ -12038,10 +12038,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>8952</v>
+        <v>8922</v>
       </c>
       <c r="X50" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="Y50" t="n">
         <v>21</v>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>115758</v>
+        <v>116012</v>
       </c>
       <c r="X51" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="Y51" t="n">
         <v>18</v>
@@ -12502,10 +12502,10 @@
         <v>0.082</v>
       </c>
       <c r="W52" t="n">
-        <v>1664</v>
+        <v>1671</v>
       </c>
       <c r="X52" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="Y52" t="n">
         <v>39</v>
@@ -13116,105 +13116,105 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>260.4</v>
+        <v>58.16</v>
       </c>
       <c r="D13" t="n">
-        <v>243.52</v>
+        <v>53.59</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="F13" t="n">
-        <v>67.65000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="G13" t="n">
-        <v>1.11</v>
+        <v>2.01</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5119.5</v>
+        <v>260.4</v>
       </c>
       <c r="D14" t="n">
-        <v>5198.76</v>
+        <v>243.52</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5</v>
+        <v>6.9</v>
       </c>
       <c r="F14" t="n">
-        <v>67.16</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>7.21</v>
+        <v>1.11</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>58.16</v>
+        <v>5119.5</v>
       </c>
       <c r="D15" t="n">
-        <v>53.45</v>
+        <v>5198.76</v>
       </c>
       <c r="E15" t="n">
-        <v>8.800000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="F15" t="n">
-        <v>67.23</v>
+        <v>67.16</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>7.21</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
@@ -13711,105 +13711,105 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>272.8</v>
+        <v>201.07</v>
       </c>
       <c r="D30" t="n">
-        <v>269.7</v>
+        <v>191.87</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="F30" t="n">
-        <v>73.09</v>
+        <v>70.02</v>
       </c>
       <c r="G30" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>51.92</v>
+        <v>272.8</v>
       </c>
       <c r="D31" t="n">
-        <v>55.69</v>
+        <v>269.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.8</v>
+        <v>1.1</v>
       </c>
       <c r="F31" t="n">
-        <v>73.01000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="G31" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>201.07</v>
+        <v>51.92</v>
       </c>
       <c r="D32" t="n">
-        <v>191.87</v>
+        <v>55.69</v>
       </c>
       <c r="E32" t="n">
-        <v>4.8</v>
+        <v>-6.8</v>
       </c>
       <c r="F32" t="n">
-        <v>70.02</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
@@ -14283,23 +14283,23 @@
         <v>95.14</v>
       </c>
       <c r="D46" t="n">
-        <v>98.83</v>
+        <v>97.5</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.7</v>
+        <v>-2.4</v>
       </c>
       <c r="F46" t="n">
         <v>71.89</v>
       </c>
       <c r="G46" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
